--- a/my_barcode_app/categories.xlsx
+++ b/my_barcode_app/categories.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF84853B-79E6-463C-AE9D-5004111743C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3FD74C-2A2A-41FF-84ED-39EC007A9C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="691">
   <si>
     <t>品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1729,195 +1729,9 @@
     <t>04</t>
   </si>
   <si>
-    <t>*0000020040321*</t>
-  </si>
-  <si>
     <t>05</t>
   </si>
   <si>
-    <t>*0000020147334*</t>
-  </si>
-  <si>
-    <t>*0000020150044*</t>
-  </si>
-  <si>
-    <t>*0000020159474*</t>
-  </si>
-  <si>
-    <t>*0000020159870*</t>
-  </si>
-  <si>
-    <t>*0000020169381*</t>
-  </si>
-  <si>
-    <t>*0000020248062*</t>
-  </si>
-  <si>
-    <t>*0000020430603*</t>
-  </si>
-  <si>
-    <t>*0000020310035*</t>
-  </si>
-  <si>
-    <t>*0000020314606*</t>
-  </si>
-  <si>
-    <t>*0000020119997*</t>
-  </si>
-  <si>
-    <t>*0000020320164*</t>
-  </si>
-  <si>
-    <t>*0000020395858*</t>
-  </si>
-  <si>
-    <t>*0000020395902*</t>
-  </si>
-  <si>
-    <t>*0000020433901*</t>
-  </si>
-  <si>
-    <t>*0000020561550*</t>
-  </si>
-  <si>
-    <t>*0000020591397*</t>
-  </si>
-  <si>
-    <t>*0000020600815*</t>
-  </si>
-  <si>
-    <t>*0000020247850*</t>
-  </si>
-  <si>
-    <t>*0000020557003*</t>
-  </si>
-  <si>
-    <t>*0000020592196*</t>
-  </si>
-  <si>
-    <t>*0000020592202*</t>
-  </si>
-  <si>
-    <t>*0000020592219*</t>
-  </si>
-  <si>
-    <t>*0000020592226*</t>
-  </si>
-  <si>
-    <t>*0000020592233*</t>
-  </si>
-  <si>
-    <t>*0000020592240*</t>
-  </si>
-  <si>
-    <t>*0000020592257*</t>
-  </si>
-  <si>
-    <t>*0000020592264*</t>
-  </si>
-  <si>
-    <t>*0000020592271*</t>
-  </si>
-  <si>
-    <t>*0000020592288*</t>
-  </si>
-  <si>
-    <t>*0000020698454*</t>
-  </si>
-  <si>
-    <t>*0000020715885*</t>
-  </si>
-  <si>
-    <t>*0000020797812*</t>
-  </si>
-  <si>
-    <t>*0000020834029*</t>
-  </si>
-  <si>
-    <t>*0000020871086*</t>
-  </si>
-  <si>
-    <t>*0000020851439*</t>
-  </si>
-  <si>
-    <t>*0000020893002*</t>
-  </si>
-  <si>
-    <t>*0000020894689*</t>
-  </si>
-  <si>
-    <t>*0000020894702*</t>
-  </si>
-  <si>
-    <t>*0000020894832*</t>
-  </si>
-  <si>
-    <t>*0000020909611*</t>
-  </si>
-  <si>
-    <t>*0000020916169*</t>
-  </si>
-  <si>
-    <t>*0000020916244*</t>
-  </si>
-  <si>
-    <t>*0000020916756*</t>
-  </si>
-  <si>
-    <t>*0000021051098*</t>
-  </si>
-  <si>
-    <t>*0000021052873*</t>
-  </si>
-  <si>
-    <t>*0000021057472*</t>
-  </si>
-  <si>
-    <t>*0000021059674*</t>
-  </si>
-  <si>
-    <t>*0000021078545*</t>
-  </si>
-  <si>
-    <t>*0000021078743*</t>
-  </si>
-  <si>
-    <t>*0000021078767*</t>
-  </si>
-  <si>
-    <t>*0000021162848*</t>
-  </si>
-  <si>
-    <t>*0000021165894*</t>
-  </si>
-  <si>
-    <t>*0000021168765*</t>
-  </si>
-  <si>
-    <t>*0000021193354*</t>
-  </si>
-  <si>
-    <t>*0000021204067*</t>
-  </si>
-  <si>
-    <t>*0000021218774*</t>
-  </si>
-  <si>
-    <t>*0000021258473*</t>
-  </si>
-  <si>
-    <t>*0000021258503*</t>
-  </si>
-  <si>
-    <t>*0000021258787*</t>
-  </si>
-  <si>
-    <t>*0000021277528*</t>
-  </si>
-  <si>
-    <t>*0000021277535*</t>
-  </si>
-  <si>
     <t>02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1932,6 +1746,654 @@
   <si>
     <t>*29320011*</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9310099</t>
+  </si>
+  <si>
+    <t>9310130</t>
+  </si>
+  <si>
+    <t>9310108</t>
+  </si>
+  <si>
+    <t>9310126</t>
+  </si>
+  <si>
+    <t>9310017</t>
+  </si>
+  <si>
+    <t>9310085</t>
+  </si>
+  <si>
+    <t>9310021</t>
+  </si>
+  <si>
+    <t>9310112</t>
+  </si>
+  <si>
+    <t>8010305</t>
+  </si>
+  <si>
+    <t>8010319</t>
+  </si>
+  <si>
+    <t>7221137</t>
+  </si>
+  <si>
+    <t>7221169</t>
+  </si>
+  <si>
+    <t>7220995</t>
+  </si>
+  <si>
+    <t>1208545</t>
+  </si>
+  <si>
+    <t>0561554</t>
+  </si>
+  <si>
+    <t>0433907</t>
+  </si>
+  <si>
+    <t>0698450</t>
+  </si>
+  <si>
+    <t>0317018</t>
+  </si>
+  <si>
+    <t>0150040</t>
+  </si>
+  <si>
+    <t>0159876</t>
+  </si>
+  <si>
+    <t>0159476</t>
+  </si>
+  <si>
+    <t>0715886</t>
+  </si>
+  <si>
+    <t>1258477</t>
+  </si>
+  <si>
+    <t>0684009</t>
+  </si>
+  <si>
+    <t>1182206</t>
+  </si>
+  <si>
+    <t>0147336</t>
+  </si>
+  <si>
+    <t>0931464</t>
+  </si>
+  <si>
+    <t>0511422</t>
+  </si>
+  <si>
+    <t>0510785</t>
+  </si>
+  <si>
+    <t>0540609</t>
+  </si>
+  <si>
+    <t>1123428</t>
+  </si>
+  <si>
+    <t>0346972</t>
+  </si>
+  <si>
+    <t>0535925</t>
+  </si>
+  <si>
+    <t>0510303</t>
+  </si>
+  <si>
+    <t>0633244</t>
+  </si>
+  <si>
+    <t>0683794</t>
+  </si>
+  <si>
+    <t>0733129</t>
+  </si>
+  <si>
+    <t>0814260</t>
+  </si>
+  <si>
+    <t>0646835</t>
+  </si>
+  <si>
+    <t>0646803</t>
+  </si>
+  <si>
+    <t>0654676</t>
+  </si>
+  <si>
+    <t>1257499</t>
+  </si>
+  <si>
+    <t>0797816</t>
+  </si>
+  <si>
+    <t>0646780</t>
+  </si>
+  <si>
+    <t>0894834</t>
+  </si>
+  <si>
+    <t>0646867</t>
+  </si>
+  <si>
+    <t>0535898</t>
+  </si>
+  <si>
+    <t>1187288</t>
+  </si>
+  <si>
+    <t>0987156</t>
+  </si>
+  <si>
+    <t>0877692</t>
+  </si>
+  <si>
+    <t>0511113</t>
+  </si>
+  <si>
+    <t>0646817</t>
+  </si>
+  <si>
+    <t>0633167</t>
+  </si>
+  <si>
+    <t>1257449</t>
+  </si>
+  <si>
+    <t>0644960</t>
+  </si>
+  <si>
+    <t>1078766</t>
+  </si>
+  <si>
+    <t>0633208</t>
+  </si>
+  <si>
+    <t>0646853</t>
+  </si>
+  <si>
+    <t>0346986</t>
+  </si>
+  <si>
+    <t>0771793</t>
+  </si>
+  <si>
+    <t>1078748</t>
+  </si>
+  <si>
+    <t>0916751</t>
+  </si>
+  <si>
+    <t>0894707</t>
+  </si>
+  <si>
+    <t>0894684</t>
+  </si>
+  <si>
+    <t>0646794</t>
+  </si>
+  <si>
+    <t>0646776</t>
+  </si>
+  <si>
+    <t>0893006</t>
+  </si>
+  <si>
+    <t>1258786</t>
+  </si>
+  <si>
+    <t>1258504</t>
+  </si>
+  <si>
+    <t>0646849</t>
+  </si>
+  <si>
+    <t>1078548</t>
+  </si>
+  <si>
+    <t>0646821</t>
+  </si>
+  <si>
+    <t>0540786</t>
+  </si>
+  <si>
+    <t>1187424</t>
+  </si>
+  <si>
+    <t>1081484</t>
+  </si>
+  <si>
+    <t>0320168</t>
+  </si>
+  <si>
+    <t>0052862</t>
+  </si>
+  <si>
+    <t>1186737</t>
+  </si>
+  <si>
+    <t>1125393</t>
+  </si>
+  <si>
+    <t>1107973</t>
+  </si>
+  <si>
+    <t>1108074</t>
+  </si>
+  <si>
+    <t>1108438</t>
+  </si>
+  <si>
+    <t>0310034</t>
+  </si>
+  <si>
+    <t>1367294</t>
+  </si>
+  <si>
+    <t>0314606</t>
+  </si>
+  <si>
+    <t>0040322</t>
+  </si>
+  <si>
+    <t>0591391</t>
+  </si>
+  <si>
+    <t>0395858</t>
+  </si>
+  <si>
+    <t>0395903</t>
+  </si>
+  <si>
+    <t>1164381</t>
+  </si>
+  <si>
+    <t>1188466</t>
+  </si>
+  <si>
+    <t>0867463</t>
+  </si>
+  <si>
+    <t>1077574</t>
+  </si>
+  <si>
+    <t>0807407</t>
+  </si>
+  <si>
+    <t>0957187</t>
+  </si>
+  <si>
+    <t>0934149</t>
+  </si>
+  <si>
+    <t>1265921</t>
+  </si>
+  <si>
+    <t>0843924</t>
+  </si>
+  <si>
+    <t>0975939</t>
+  </si>
+  <si>
+    <t>0841586</t>
+  </si>
+  <si>
+    <t>0873202</t>
+  </si>
+  <si>
+    <t>0987556</t>
+  </si>
+  <si>
+    <t>1041690</t>
+  </si>
+  <si>
+    <t>0169382</t>
+  </si>
+  <si>
+    <t>0806051</t>
+  </si>
+  <si>
+    <t>1140379</t>
+  </si>
+  <si>
+    <t>0806188</t>
+  </si>
+  <si>
+    <t>0600813</t>
+  </si>
+  <si>
+    <t>0804568</t>
+  </si>
+  <si>
+    <t>0805996</t>
+  </si>
+  <si>
+    <t>1375158</t>
+  </si>
+  <si>
+    <t>0287869</t>
+  </si>
+  <si>
+    <t>1072910</t>
+  </si>
+  <si>
+    <t>0240146</t>
+  </si>
+  <si>
+    <t>1277520</t>
+  </si>
+  <si>
+    <t>1277534</t>
+  </si>
+  <si>
+    <t>0899389</t>
+  </si>
+  <si>
+    <t>1038786</t>
+  </si>
+  <si>
+    <t>0615379</t>
+  </si>
+  <si>
+    <t>1167898</t>
+  </si>
+  <si>
+    <t>1077629</t>
+  </si>
+  <si>
+    <t>1254182</t>
+  </si>
+  <si>
+    <t>0248067</t>
+  </si>
+  <si>
+    <t>0916242</t>
+  </si>
+  <si>
+    <t>0615456</t>
+  </si>
+  <si>
+    <t>0615260</t>
+  </si>
+  <si>
+    <t>1092500</t>
+  </si>
+  <si>
+    <t>0663372</t>
+  </si>
+  <si>
+    <t>1218774</t>
+  </si>
+  <si>
+    <t>0909611</t>
+  </si>
+  <si>
+    <t>0916165</t>
+  </si>
+  <si>
+    <t>1057475</t>
+  </si>
+  <si>
+    <t>1204064</t>
+  </si>
+  <si>
+    <t>0615165</t>
+  </si>
+  <si>
+    <t>1162434</t>
+  </si>
+  <si>
+    <t>0873975</t>
+  </si>
+  <si>
+    <t>0873943</t>
+  </si>
+  <si>
+    <t>0615474</t>
+  </si>
+  <si>
+    <t>0615365</t>
+  </si>
+  <si>
+    <t>1107882</t>
+  </si>
+  <si>
+    <t>1002107</t>
+  </si>
+  <si>
+    <t>0852761</t>
+  </si>
+  <si>
+    <t>0615151</t>
+  </si>
+  <si>
+    <t>0837753</t>
+  </si>
+  <si>
+    <t>1066317</t>
+  </si>
+  <si>
+    <t>1193354</t>
+  </si>
+  <si>
+    <t>1135063</t>
+  </si>
+  <si>
+    <t>1278221</t>
+  </si>
+  <si>
+    <t>1101672</t>
+  </si>
+  <si>
+    <t>1216681</t>
+  </si>
+  <si>
+    <t>1052875</t>
+  </si>
+  <si>
+    <t>0853612</t>
+  </si>
+  <si>
+    <t>1045276</t>
+  </si>
+  <si>
+    <t>0916606</t>
+  </si>
+  <si>
+    <t>1290754</t>
+  </si>
+  <si>
+    <t>1165896</t>
+  </si>
+  <si>
+    <t>0659571</t>
+  </si>
+  <si>
+    <t>0309918</t>
+  </si>
+  <si>
+    <t>0886516</t>
+  </si>
+  <si>
+    <t>0794909</t>
+  </si>
+  <si>
+    <t>1051097</t>
+  </si>
+  <si>
+    <t>0250725</t>
+  </si>
+  <si>
+    <t>0975466</t>
+  </si>
+  <si>
+    <t>0979533</t>
+  </si>
+  <si>
+    <t>1231217</t>
+  </si>
+  <si>
+    <t>0945910</t>
+  </si>
+  <si>
+    <t>0871082</t>
+  </si>
+  <si>
+    <t>1114772</t>
+  </si>
+  <si>
+    <t>1112457</t>
+  </si>
+  <si>
+    <t>1071732</t>
+  </si>
+  <si>
+    <t>1162848</t>
+  </si>
+  <si>
+    <t>0945924</t>
+  </si>
+  <si>
+    <t>0933270</t>
+  </si>
+  <si>
+    <t>0248130</t>
+  </si>
+  <si>
+    <t>1181432</t>
+  </si>
+  <si>
+    <t>0988239</t>
+  </si>
+  <si>
+    <t>1221610</t>
+  </si>
+  <si>
+    <t>0566168</t>
+  </si>
+  <si>
+    <t>1112675</t>
+  </si>
+  <si>
+    <t>0410050</t>
+  </si>
+  <si>
+    <t>1139926</t>
+  </si>
+  <si>
+    <t>1221701</t>
+  </si>
+  <si>
+    <t>1146402</t>
+  </si>
+  <si>
+    <t>0396109</t>
+  </si>
+  <si>
+    <t>1333671</t>
+  </si>
+  <si>
+    <t>0414804</t>
+  </si>
+  <si>
+    <t>1316811</t>
+  </si>
+  <si>
+    <t>0247120</t>
+  </si>
+  <si>
+    <t>1071150</t>
+  </si>
+  <si>
+    <t>0887067</t>
+  </si>
+  <si>
+    <t>0959775</t>
+  </si>
+  <si>
+    <t>1059677</t>
+  </si>
+  <si>
+    <t>1059704</t>
+  </si>
+  <si>
+    <t>0874399</t>
+  </si>
+  <si>
+    <t>1108501</t>
+  </si>
+  <si>
+    <t>1109466</t>
+  </si>
+  <si>
+    <t>1359130</t>
+  </si>
+  <si>
+    <t>1397936</t>
+  </si>
+  <si>
+    <t>0821487</t>
+  </si>
+  <si>
+    <t>0318478</t>
+  </si>
+  <si>
+    <t>7637582</t>
+  </si>
+  <si>
+    <t>7637019</t>
+  </si>
+  <si>
+    <t>7630021</t>
+  </si>
+  <si>
+    <t>7630067</t>
+  </si>
+  <si>
+    <t>7630508</t>
+  </si>
+  <si>
+    <t>7630526</t>
+  </si>
+  <si>
+    <t>7630308</t>
+  </si>
+  <si>
+    <t>7630635</t>
+  </si>
+  <si>
+    <t>8551036</t>
+  </si>
+  <si>
+    <t>0007958</t>
+  </si>
+  <si>
+    <t>1168767</t>
+  </si>
+  <si>
+    <t>1077251</t>
+  </si>
+  <si>
+    <t>1077233</t>
+  </si>
+  <si>
+    <t>0868487</t>
+  </si>
+  <si>
+    <t>0440706</t>
+  </si>
+  <si>
+    <t>0783356</t>
   </si>
 </sst>
 </file>
@@ -2344,13 +2806,13 @@
         <v>305</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>536</v>
+        <v>474</v>
       </c>
       <c r="D2" s="4" t="e">
         <v>#N/A</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,11 +2825,11 @@
       <c r="C3" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D3" s="4" t="s">
+        <v>475</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2380,11 +2842,11 @@
       <c r="C4" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D4" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2397,11 +2859,11 @@
       <c r="C5" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D5" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D5" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2414,11 +2876,11 @@
       <c r="C6" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D6" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2431,11 +2893,11 @@
       <c r="C7" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D7" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2448,11 +2910,11 @@
       <c r="C8" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D8" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D8" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2465,11 +2927,11 @@
       <c r="C9" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D9" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D9" s="4" t="s">
+        <v>481</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,11 +2944,11 @@
       <c r="C10" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D10" s="4" t="s">
+        <v>482</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,11 +2961,11 @@
       <c r="C11" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D11" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D11" s="4" t="s">
+        <v>483</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2516,11 +2978,11 @@
       <c r="C12" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D12" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D12" s="4" t="s">
+        <v>484</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2533,11 +2995,11 @@
       <c r="C13" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D13" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D13" s="4" t="s">
+        <v>485</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2550,11 +3012,11 @@
       <c r="C14" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D14" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D14" s="4" t="s">
+        <v>486</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2567,11 +3029,11 @@
       <c r="C15" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D15" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D15" s="4" t="s">
+        <v>487</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2585,7 +3047,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>21</v>
+        <v>488</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>468</v>
@@ -2605,7 +3067,7 @@
         <v>#N/A</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>533</v>
+        <v>471</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2619,7 +3081,7 @@
         <v>420</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>468</v>
@@ -2636,7 +3098,7 @@
         <v>422</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>468</v>
@@ -2653,7 +3115,7 @@
         <v>423</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>468</v>
@@ -2670,7 +3132,7 @@
         <v>427</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>468</v>
@@ -2687,7 +3149,7 @@
         <v>444</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>468</v>
@@ -2704,7 +3166,7 @@
         <v>445</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>468</v>
@@ -2721,7 +3183,7 @@
         <v>446</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>468</v>
@@ -2738,7 +3200,7 @@
         <v>421</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>467</v>
@@ -2755,7 +3217,7 @@
         <v>278</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>528</v>
+        <v>497</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>469</v>
@@ -2772,7 +3234,7 @@
         <v>316</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>316</v>
+        <v>498</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>469</v>
@@ -2789,7 +3251,7 @@
         <v>317</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>317</v>
+        <v>499</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>469</v>
@@ -2806,7 +3268,7 @@
         <v>319</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>469</v>
@@ -2823,7 +3285,7 @@
         <v>320</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>320</v>
+        <v>501</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>469</v>
@@ -2840,7 +3302,7 @@
         <v>321</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>321</v>
+        <v>502</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>469</v>
@@ -2857,7 +3319,7 @@
         <v>322</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>322</v>
+        <v>503</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>469</v>
@@ -2874,7 +3336,7 @@
         <v>323</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>323</v>
+        <v>504</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>469</v>
@@ -2891,7 +3353,7 @@
         <v>324</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>324</v>
+        <v>505</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>469</v>
@@ -2908,7 +3370,7 @@
         <v>325</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>325</v>
+        <v>506</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>469</v>
@@ -2925,7 +3387,7 @@
         <v>326</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>326</v>
+        <v>507</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>469</v>
@@ -2942,7 +3404,7 @@
         <v>327</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>327</v>
+        <v>508</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>469</v>
@@ -2959,7 +3421,7 @@
         <v>328</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>328</v>
+        <v>509</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>469</v>
@@ -2976,7 +3438,7 @@
         <v>329</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>329</v>
+        <v>510</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>469</v>
@@ -2993,7 +3455,7 @@
         <v>330</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>330</v>
+        <v>511</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>469</v>
@@ -3010,7 +3472,7 @@
         <v>331</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>331</v>
+        <v>512</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>469</v>
@@ -3027,7 +3489,7 @@
         <v>332</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>469</v>
@@ -3044,7 +3506,7 @@
         <v>333</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>469</v>
@@ -3061,7 +3523,7 @@
         <v>334</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>334</v>
+        <v>515</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>469</v>
@@ -3078,7 +3540,7 @@
         <v>335</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>335</v>
+        <v>516</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>469</v>
@@ -3095,7 +3557,7 @@
         <v>336</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>469</v>
@@ -3112,7 +3574,7 @@
         <v>337</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>469</v>
@@ -3129,7 +3591,7 @@
         <v>338</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>469</v>
@@ -3146,7 +3608,7 @@
         <v>339</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>469</v>
@@ -3163,7 +3625,7 @@
         <v>340</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>340</v>
+        <v>521</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>469</v>
@@ -3180,7 +3642,7 @@
         <v>341</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>341</v>
+        <v>522</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>469</v>
@@ -3197,7 +3659,7 @@
         <v>342</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>342</v>
+        <v>523</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>469</v>
@@ -3214,7 +3676,7 @@
         <v>343</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>343</v>
+        <v>524</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>469</v>
@@ -3231,7 +3693,7 @@
         <v>344</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>344</v>
+        <v>525</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>469</v>
@@ -3248,7 +3710,7 @@
         <v>346</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>469</v>
@@ -3265,7 +3727,7 @@
         <v>347</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>347</v>
+        <v>527</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>469</v>
@@ -3282,7 +3744,7 @@
         <v>348</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>348</v>
+        <v>528</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>469</v>
@@ -3299,7 +3761,7 @@
         <v>349</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>349</v>
+        <v>529</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>469</v>
@@ -3316,7 +3778,7 @@
         <v>350</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>469</v>
@@ -3333,7 +3795,7 @@
         <v>351</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>351</v>
+        <v>531</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>469</v>
@@ -3350,7 +3812,7 @@
         <v>352</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>469</v>
@@ -3367,7 +3829,7 @@
         <v>353</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>353</v>
+        <v>533</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>469</v>
@@ -3384,7 +3846,7 @@
         <v>354</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>354</v>
+        <v>534</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>469</v>
@@ -3401,7 +3863,7 @@
         <v>355</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>469</v>
@@ -3418,7 +3880,7 @@
         <v>356</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>469</v>
@@ -3435,7 +3897,7 @@
         <v>357</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>469</v>
@@ -3452,7 +3914,7 @@
         <v>358</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>469</v>
@@ -3469,7 +3931,7 @@
         <v>359</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>493</v>
+        <v>539</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>469</v>
@@ -3486,7 +3948,7 @@
         <v>360</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>491</v>
+        <v>540</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>469</v>
@@ -3503,7 +3965,7 @@
         <v>361</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>469</v>
@@ -3520,7 +3982,7 @@
         <v>362</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>469</v>
@@ -3537,7 +3999,7 @@
         <v>363</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>469</v>
@@ -3554,7 +4016,7 @@
         <v>364</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>498</v>
+        <v>544</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>469</v>
@@ -3571,7 +4033,7 @@
         <v>365</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>469</v>
@@ -3588,7 +4050,7 @@
         <v>366</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>496</v>
+        <v>546</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>469</v>
@@ -3605,7 +4067,7 @@
         <v>367</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>367</v>
+        <v>547</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>469</v>
@@ -3622,10 +4084,10 @@
         <v>155</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>155</v>
+        <v>548</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3639,10 +4101,10 @@
         <v>156</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>156</v>
+        <v>549</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3656,10 +4118,10 @@
         <v>157</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>482</v>
+        <v>550</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3673,10 +4135,10 @@
         <v>158</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>158</v>
+        <v>551</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3690,10 +4152,10 @@
         <v>159</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>159</v>
+        <v>552</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3707,10 +4169,10 @@
         <v>160</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>160</v>
+        <v>553</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3724,10 +4186,10 @@
         <v>161</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>161</v>
+        <v>554</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3741,10 +4203,10 @@
         <v>162</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>162</v>
+        <v>555</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3758,10 +4220,10 @@
         <v>163</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>163</v>
+        <v>556</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3775,10 +4237,10 @@
         <v>164</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3791,11 +4253,11 @@
       <c r="C87" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D87" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D87" s="4" t="s">
+        <v>558</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3809,10 +4271,10 @@
         <v>166</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>480</v>
+        <v>559</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3826,10 +4288,10 @@
         <v>167</v>
       </c>
       <c r="D89" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3843,10 +4305,10 @@
         <v>168</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>487</v>
+        <v>561</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3860,10 +4322,10 @@
         <v>169</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>483</v>
+        <v>562</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3877,10 +4339,10 @@
         <v>170</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>484</v>
+        <v>563</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3894,10 +4356,10 @@
         <v>171</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>171</v>
+        <v>564</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3911,10 +4373,10 @@
         <v>172</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>172</v>
+        <v>565</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3928,10 +4390,10 @@
         <v>173</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>173</v>
+        <v>566</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3945,10 +4407,10 @@
         <v>174</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>174</v>
+        <v>567</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -3962,10 +4424,10 @@
         <v>175</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>175</v>
+        <v>568</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -3979,10 +4441,10 @@
         <v>176</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>176</v>
+        <v>569</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -3996,10 +4458,10 @@
         <v>177</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>177</v>
+        <v>570</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4013,10 +4475,10 @@
         <v>178</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>178</v>
+        <v>571</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4030,10 +4492,10 @@
         <v>179</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>179</v>
+        <v>572</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4047,10 +4509,10 @@
         <v>180</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>180</v>
+        <v>573</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4064,10 +4526,10 @@
         <v>181</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>181</v>
+        <v>574</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4081,10 +4543,10 @@
         <v>182</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>182</v>
+        <v>575</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4098,10 +4560,10 @@
         <v>183</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>183</v>
+        <v>576</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4115,10 +4577,10 @@
         <v>184</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>184</v>
+        <v>577</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4132,10 +4594,10 @@
         <v>185</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>476</v>
+        <v>578</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4149,10 +4611,10 @@
         <v>186</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>186</v>
+        <v>579</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4166,10 +4628,10 @@
         <v>187</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>187</v>
+        <v>580</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -4186,7 +4648,7 @@
         <v>#N/A</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -4200,10 +4662,10 @@
         <v>189</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>189</v>
+        <v>581</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -4217,10 +4679,10 @@
         <v>190</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>488</v>
+        <v>582</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -4234,10 +4696,10 @@
         <v>191</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>191</v>
+        <v>583</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -4251,10 +4713,10 @@
         <v>192</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>192</v>
+        <v>584</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -4267,11 +4729,11 @@
       <c r="C115" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D115" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D115" s="4" t="s">
+        <v>585</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -4285,7 +4747,7 @@
         <v>13</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>478</v>
+        <v>586</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>15</v>
@@ -4302,7 +4764,7 @@
         <v>16</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>15</v>
@@ -4319,7 +4781,7 @@
         <v>17</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>15</v>
@@ -4336,7 +4798,7 @@
         <v>18</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>531</v>
+        <v>589</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>15</v>
@@ -4353,7 +4815,7 @@
         <v>19</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>532</v>
+        <v>590</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>15</v>
@@ -4370,7 +4832,7 @@
         <v>20</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>20</v>
+        <v>591</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>15</v>
@@ -4387,7 +4849,7 @@
         <v>22</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>22</v>
+        <v>592</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>15</v>
@@ -4404,7 +4866,7 @@
         <v>23</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>23</v>
+        <v>593</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>15</v>
@@ -4421,7 +4883,7 @@
         <v>24</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>24</v>
+        <v>594</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>15</v>
@@ -4438,7 +4900,7 @@
         <v>25</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>25</v>
+        <v>595</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>15</v>
@@ -4455,7 +4917,7 @@
         <v>26</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>26</v>
+        <v>596</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>15</v>
@@ -4472,7 +4934,7 @@
         <v>27</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>477</v>
+        <v>597</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>15</v>
@@ -4489,7 +4951,7 @@
         <v>28</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>513</v>
+        <v>598</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>15</v>
@@ -4506,7 +4968,7 @@
         <v>29</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>29</v>
+        <v>599</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>15</v>
@@ -4523,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>15</v>
@@ -4540,7 +5002,7 @@
         <v>31</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>31</v>
+        <v>601</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>15</v>
@@ -4557,7 +5019,7 @@
         <v>32</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>32</v>
+        <v>602</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>15</v>
@@ -4574,7 +5036,7 @@
         <v>33</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>527</v>
+        <v>603</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>15</v>
@@ -4591,7 +5053,7 @@
         <v>34</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>511</v>
+        <v>604</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>15</v>
@@ -4608,7 +5070,7 @@
         <v>35</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>512</v>
+        <v>605</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>15</v>
@@ -4625,7 +5087,7 @@
         <v>36</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>517</v>
+        <v>606</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>15</v>
@@ -4642,7 +5104,7 @@
         <v>37</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>526</v>
+        <v>607</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>15</v>
@@ -4659,7 +5121,7 @@
         <v>38</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>38</v>
+        <v>608</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>15</v>
@@ -4676,7 +5138,7 @@
         <v>39</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>39</v>
+        <v>609</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>15</v>
@@ -4693,7 +5155,7 @@
         <v>40</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>40</v>
+        <v>610</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>15</v>
@@ -4710,7 +5172,7 @@
         <v>41</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>41</v>
+        <v>611</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>15</v>
@@ -4727,7 +5189,7 @@
         <v>42</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>490</v>
+        <v>612</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>15</v>
@@ -4744,7 +5206,7 @@
         <v>43</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>43</v>
+        <v>613</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>15</v>
@@ -4761,7 +5223,7 @@
         <v>44</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>44</v>
+        <v>614</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>15</v>
@@ -4778,7 +5240,7 @@
         <v>45</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>45</v>
+        <v>615</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>15</v>
@@ -4795,7 +5257,7 @@
         <v>46</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>46</v>
+        <v>616</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>15</v>
@@ -4812,7 +5274,7 @@
         <v>47</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>489</v>
+        <v>617</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>15</v>
@@ -4829,7 +5291,7 @@
         <v>48</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>48</v>
+        <v>618</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>15</v>
@@ -4846,7 +5308,7 @@
         <v>49</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>49</v>
+        <v>619</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>15</v>
@@ -4863,7 +5325,7 @@
         <v>50</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>525</v>
+        <v>620</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>15</v>
@@ -4880,7 +5342,7 @@
         <v>51</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>51</v>
+        <v>621</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>15</v>
@@ -4897,7 +5359,7 @@
         <v>52</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>52</v>
+        <v>622</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>15</v>
@@ -4914,7 +5376,7 @@
         <v>53</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>53</v>
+        <v>623</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>15</v>
@@ -4931,7 +5393,7 @@
         <v>54</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>54</v>
+        <v>624</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>15</v>
@@ -4948,7 +5410,7 @@
         <v>55</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>516</v>
+        <v>625</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>15</v>
@@ -4965,7 +5427,7 @@
         <v>56</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>504</v>
+        <v>626</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>15</v>
@@ -4982,7 +5444,7 @@
         <v>57</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>57</v>
+        <v>627</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>15</v>
@@ -4999,7 +5461,7 @@
         <v>58</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>58</v>
+        <v>628</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>15</v>
@@ -5016,7 +5478,7 @@
         <v>59</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>59</v>
+        <v>629</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>15</v>
@@ -5033,7 +5495,7 @@
         <v>60</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>523</v>
+        <v>630</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>15</v>
@@ -5050,7 +5512,7 @@
         <v>61</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>61</v>
+        <v>631</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>15</v>
@@ -5067,7 +5529,7 @@
         <v>62</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>62</v>
+        <v>632</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>15</v>
@@ -5084,7 +5546,7 @@
         <v>63</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>63</v>
+        <v>633</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>15</v>
@@ -5101,7 +5563,7 @@
         <v>64</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>64</v>
+        <v>634</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>15</v>
@@ -5118,7 +5580,7 @@
         <v>65</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>515</v>
+        <v>635</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>15</v>
@@ -5135,7 +5597,7 @@
         <v>66</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>66</v>
+        <v>636</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>15</v>
@@ -5152,7 +5614,7 @@
         <v>67</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>67</v>
+        <v>637</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>15</v>
@@ -5169,7 +5631,7 @@
         <v>68</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>68</v>
+        <v>638</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>15</v>
@@ -5186,7 +5648,7 @@
         <v>69</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>69</v>
+        <v>639</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>15</v>
@@ -5203,7 +5665,7 @@
         <v>70</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>70</v>
+        <v>640</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>15</v>
@@ -5220,7 +5682,7 @@
         <v>71</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>505</v>
+        <v>641</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>15</v>
@@ -5237,7 +5699,7 @@
         <v>72</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>72</v>
+        <v>642</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>15</v>
@@ -5254,7 +5716,7 @@
         <v>73</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>73</v>
+        <v>643</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5733,7 @@
         <v>74</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>74</v>
+        <v>644</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>15</v>
@@ -5288,7 +5750,7 @@
         <v>75</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>522</v>
+        <v>645</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>15</v>
@@ -5305,7 +5767,7 @@
         <v>76</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>76</v>
+        <v>646</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>15</v>
@@ -5322,7 +5784,7 @@
         <v>77</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>77</v>
+        <v>647</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>15</v>
@@ -5339,7 +5801,7 @@
         <v>78</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>78</v>
+        <v>648</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>15</v>
@@ -5356,7 +5818,7 @@
         <v>79</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>79</v>
+        <v>649</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>15</v>
@@ -5373,7 +5835,7 @@
         <v>80</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>80</v>
+        <v>650</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>15</v>
@@ -5390,7 +5852,7 @@
         <v>81</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>81</v>
+        <v>651</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>15</v>
@@ -5407,7 +5869,7 @@
         <v>82</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>82</v>
+        <v>652</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>15</v>
@@ -5424,7 +5886,7 @@
         <v>83</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>83</v>
+        <v>653</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>15</v>
@@ -5458,7 +5920,7 @@
         <v>231</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>231</v>
+        <v>654</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>15</v>
@@ -5475,7 +5937,7 @@
         <v>232</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>232</v>
+        <v>655</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>15</v>
@@ -5492,7 +5954,7 @@
         <v>233</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>233</v>
+        <v>656</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>15</v>
@@ -5509,7 +5971,7 @@
         <v>234</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>234</v>
+        <v>657</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>15</v>
@@ -5526,7 +5988,7 @@
         <v>235</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>235</v>
+        <v>658</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>15</v>
@@ -5542,8 +6004,8 @@
       <c r="C190" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D190" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D190" s="4" t="s">
+        <v>659</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>15</v>
@@ -5560,7 +6022,7 @@
         <v>237</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>237</v>
+        <v>660</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>15</v>
@@ -5577,7 +6039,7 @@
         <v>238</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>238</v>
+        <v>661</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>15</v>
@@ -5594,7 +6056,7 @@
         <v>239</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>239</v>
+        <v>662</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>15</v>
@@ -5611,7 +6073,7 @@
         <v>240</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>240</v>
+        <v>663</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>15</v>
@@ -5628,7 +6090,7 @@
         <v>241</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>241</v>
+        <v>664</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>15</v>
@@ -5645,7 +6107,7 @@
         <v>242</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>242</v>
+        <v>665</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>15</v>
@@ -5662,7 +6124,7 @@
         <v>243</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>518</v>
+        <v>666</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>15</v>
@@ -5679,7 +6141,7 @@
         <v>244</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>244</v>
+        <v>667</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>15</v>
@@ -5696,7 +6158,7 @@
         <v>245</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>506</v>
+        <v>668</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>15</v>
@@ -5730,7 +6192,7 @@
         <v>247</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>247</v>
+        <v>669</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>15</v>
@@ -5747,7 +6209,7 @@
         <v>248</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>248</v>
+        <v>670</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>15</v>
@@ -5763,8 +6225,8 @@
       <c r="C203" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D203" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D203" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>15</v>
@@ -5780,8 +6242,8 @@
       <c r="C204" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D204" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D204" s="4" t="s">
+        <v>672</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>15</v>
@@ -5815,7 +6277,7 @@
         <v>345</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>345</v>
+        <v>673</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>469</v>
@@ -5832,7 +6294,7 @@
         <v>428</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>428</v>
+        <v>674</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>15</v>
@@ -5848,11 +6310,11 @@
       <c r="C208" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D208" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D208" s="4" t="s">
+        <v>675</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -5865,11 +6327,11 @@
       <c r="C209" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D209" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D209" s="4" t="s">
+        <v>676</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -5882,11 +6344,11 @@
       <c r="C210" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D210" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D210" s="4" t="s">
+        <v>677</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -5899,11 +6361,11 @@
       <c r="C211" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D211" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D211" s="4" t="s">
+        <v>678</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -5916,11 +6378,11 @@
       <c r="C212" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D212" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D212" s="4" t="s">
+        <v>679</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -5933,11 +6395,11 @@
       <c r="C213" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D213" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D213" s="4" t="s">
+        <v>680</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -5950,11 +6412,11 @@
       <c r="C214" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D214" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D214" s="4" t="s">
+        <v>681</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -5967,11 +6429,11 @@
       <c r="C215" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D215" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D215" s="4" t="s">
+        <v>682</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -5984,11 +6446,11 @@
       <c r="C216" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D216" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D216" s="4" t="s">
+        <v>683</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="14.25" x14ac:dyDescent="0.25">
@@ -6005,7 +6467,7 @@
         <v>#N/A</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="14.25" x14ac:dyDescent="0.25">
@@ -6022,7 +6484,7 @@
         <v>#N/A</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6036,7 +6498,7 @@
         <v>318</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>318</v>
+        <v>684</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>466</v>
@@ -6053,7 +6515,7 @@
         <v>424</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>524</v>
+        <v>685</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>466</v>
@@ -6070,7 +6532,7 @@
         <v>425</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>425</v>
+        <v>686</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>466</v>
@@ -6087,7 +6549,7 @@
         <v>426</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>426</v>
+        <v>687</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>466</v>
@@ -6104,7 +6566,7 @@
         <v>450</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>450</v>
+        <v>688</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>466</v>
@@ -6121,7 +6583,7 @@
         <v>452</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>452</v>
+        <v>689</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>466</v>
@@ -6137,8 +6599,8 @@
       <c r="C225" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D225" s="4" t="s">
-        <v>453</v>
+      <c r="D225" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>466</v>
@@ -6155,7 +6617,7 @@
         <v>454</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>454</v>
+        <v>690</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>466</v>
